--- a/data/trans_dic/P19C01-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19C01-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue una revisión o chequeo</t>
+          <t>Población cuyo motivo por su última visita al dentista fue una revisión o chequeo (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32,09; 42,21</t>
+          <t>31,99; 42,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,06; 42,05</t>
+          <t>31,46; 41,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45,56; 56,48</t>
+          <t>45,52; 56,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63,39; 72,17</t>
+          <t>63,59; 71,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,78; 47,11</t>
+          <t>35,35; 47,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,07; 52,25</t>
+          <t>39,9; 51,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,52; 58,74</t>
+          <t>47,32; 58,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>63,12; 70,61</t>
+          <t>62,66; 70,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,98; 42,65</t>
+          <t>34,99; 42,38</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,57; 44,89</t>
+          <t>36,68; 44,49</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48,13; 55,91</t>
+          <t>47,99; 55,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>64,28; 70,31</t>
+          <t>64,26; 70,09</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,55; 37,53</t>
+          <t>24,95; 36,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,61; 42,18</t>
+          <t>31,66; 42,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,14; 52,28</t>
+          <t>41,12; 52,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61,18; 70,03</t>
+          <t>61,45; 70,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,71; 43,52</t>
+          <t>32,31; 43,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,93; 51,88</t>
+          <t>39,76; 51,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,81; 59,45</t>
+          <t>48,39; 59,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>63,65; 71,9</t>
+          <t>63,58; 72,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,62; 38,36</t>
+          <t>30,81; 38,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37,0; 45,14</t>
+          <t>36,61; 45,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46,35; 54,59</t>
+          <t>46,45; 54,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>63,22; 69,83</t>
+          <t>63,28; 69,38</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,25; 31,67</t>
+          <t>23,18; 32,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,65; 30,67</t>
+          <t>22,76; 30,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,99; 42,45</t>
+          <t>32,92; 43,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,93; 57,75</t>
+          <t>14,16; 57,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,58; 43,06</t>
+          <t>27,54; 43,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,71; 39,14</t>
+          <t>26,58; 38,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,17; 42,53</t>
+          <t>25,86; 41,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49,43; 61,64</t>
+          <t>49,29; 61,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,38; 33,08</t>
+          <t>25,57; 32,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24,87; 31,79</t>
+          <t>25,43; 31,93</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,86; 41,33</t>
+          <t>32,46; 41,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,87; 57,66</t>
+          <t>16,68; 57,53</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,81; 26,89</t>
+          <t>21,37; 27,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,12; 26,84</t>
+          <t>21,11; 27,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,3; 39,84</t>
+          <t>33,44; 40,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48,56; 55,4</t>
+          <t>48,28; 54,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,35; 37,32</t>
+          <t>29,61; 37,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,37; 39,5</t>
+          <t>31,94; 39,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,05; 43,41</t>
+          <t>35,72; 43,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26,39; 61,37</t>
+          <t>25,14; 61,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,78; 30,57</t>
+          <t>25,66; 30,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,44; 30,93</t>
+          <t>26,67; 31,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,45; 40,46</t>
+          <t>35,31; 40,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34,08; 56,4</t>
+          <t>36,74; 56,39</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>23,14; 34,38</t>
+          <t>22,77; 34,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,43; 25,37</t>
+          <t>17,34; 25,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25,93; 34,82</t>
+          <t>25,97; 35,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41,48; 51,73</t>
+          <t>41,7; 51,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,21; 32,96</t>
+          <t>24,87; 32,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,82; 29,8</t>
+          <t>22,44; 29,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,5; 41,76</t>
+          <t>33,82; 41,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>45,69; 64,2</t>
+          <t>45,18; 62,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,42; 32,1</t>
+          <t>25,26; 32,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,57; 26,81</t>
+          <t>21,6; 26,84</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31,12; 37,34</t>
+          <t>31,43; 37,52</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>45,43; 58,5</t>
+          <t>45,34; 58,22</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37,76; 51,45</t>
+          <t>37,53; 51,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43,91; 57,6</t>
+          <t>43,94; 57,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48,56; 61,01</t>
+          <t>48,68; 61,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52,9; 75,41</t>
+          <t>54,23; 76,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23,06; 28,67</t>
+          <t>22,89; 28,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,23; 35,53</t>
+          <t>29,14; 35,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,81; 47,84</t>
+          <t>40,95; 47,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>54,33; 60,82</t>
+          <t>54,03; 61,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,52; 31,54</t>
+          <t>26,44; 31,78</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33,18; 38,55</t>
+          <t>33,2; 38,94</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>43,78; 49,76</t>
+          <t>43,7; 49,83</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>56,43; 63,42</t>
+          <t>55,7; 63,38</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27,89; 31,68</t>
+          <t>27,95; 31,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>27,66; 31,17</t>
+          <t>27,56; 31,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38,8; 42,44</t>
+          <t>38,56; 42,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40,78; 58,07</t>
+          <t>40,68; 57,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,6; 33,21</t>
+          <t>29,63; 33,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,46; 36,0</t>
+          <t>32,66; 36,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,62; 45,52</t>
+          <t>41,78; 45,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>44,64; 60,18</t>
+          <t>43,96; 60,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29,37; 31,87</t>
+          <t>29,35; 31,9</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30,63; 33,07</t>
+          <t>30,69; 33,15</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40,86; 43,43</t>
+          <t>40,78; 43,47</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,44; 58,44</t>
+          <t>47,11; 58,54</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue una revisión o chequeo</t>
+          <t>Población cuyo motivo por su última visita al dentista fue una revisión o chequeo (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>124454; 163696</t>
+          <t>124042; 162956</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>126750; 166238</t>
+          <t>124383; 165526</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>176586; 218931</t>
+          <t>176436; 218797</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>316428; 360246</t>
+          <t>317417; 359018</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>93301; 126382</t>
+          <t>94845; 127907</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>117782; 153584</t>
+          <t>117289; 151950</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>150064; 185500</t>
+          <t>149439; 184917</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>278292; 311340</t>
+          <t>276292; 310157</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>229478; 279810</t>
+          <t>229538; 278023</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>252049; 309426</t>
+          <t>252853; 306637</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>338530; 393261</t>
+          <t>337592; 392556</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>604258; 661038</t>
+          <t>604120; 658877</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>76712; 112665</t>
+          <t>74909; 109676</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>121282; 161857</t>
+          <t>121475; 161963</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>127099; 165539</t>
+          <t>130210; 165226</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>274364; 314019</t>
+          <t>275568; 316233</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>109113; 145161</t>
+          <t>107777; 145980</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>125188; 162654</t>
+          <t>124641; 160404</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>162829; 198300</t>
+          <t>161432; 198920</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>240350; 271512</t>
+          <t>240091; 272882</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>194084; 243095</t>
+          <t>195243; 245958</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>257988; 314760</t>
+          <t>255260; 313819</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>301403; 354969</t>
+          <t>302049; 355949</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>522236; 576787</t>
+          <t>522701; 573130</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>100026; 136284</t>
+          <t>99732; 138337</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>121307; 164251</t>
+          <t>121870; 162525</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>133688; 172006</t>
+          <t>133406; 174397</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>85442; 381540</t>
+          <t>93586; 382921</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>38632; 60312</t>
+          <t>38580; 61094</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64279; 94176</t>
+          <t>63962; 93028</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36486; 59291</t>
+          <t>36049; 57384</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>81541; 101691</t>
+          <t>81315; 102132</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>144748; 188640</t>
+          <t>145809; 187452</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>193055; 246761</t>
+          <t>197369; 247794</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>178987; 225083</t>
+          <t>176770; 223566</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>147574; 476109</t>
+          <t>137756; 474993</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>181324; 234321</t>
+          <t>186201; 236910</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>205452; 261041</t>
+          <t>205319; 263389</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>292836; 350361</t>
+          <t>294111; 353012</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>484708; 552987</t>
+          <t>481880; 548228</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>174699; 222176</t>
+          <t>176287; 222982</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>225929; 275715</t>
+          <t>222946; 275125</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>246565; 296950</t>
+          <t>244318; 297020</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>253064; 588487</t>
+          <t>241065; 592223</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>378094; 448459</t>
+          <t>376336; 444399</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>441735; 516681</t>
+          <t>445556; 518960</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>554327; 632594</t>
+          <t>552036; 631362</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>666896; 1103838</t>
+          <t>719083; 1103506</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>57383; 85235</t>
+          <t>56442; 85853</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>70289; 102315</t>
+          <t>69920; 101817</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>110255; 148046</t>
+          <t>110431; 149166</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>182041; 227033</t>
+          <t>183013; 227579</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>110420; 150321</t>
+          <t>113443; 150057</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>152849; 199608</t>
+          <t>150316; 197604</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>186766; 232799</t>
+          <t>188516; 233672</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>371938; 522568</t>
+          <t>367758; 509445</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>178985; 226011</t>
+          <t>177843; 228309</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>231482; 287697</t>
+          <t>231837; 288047</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>305786; 366903</t>
+          <t>308879; 368662</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>569112; 732858</t>
+          <t>568037; 729429</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>80145; 109193</t>
+          <t>79642; 109745</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>97131; 127417</t>
+          <t>97192; 126605</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>117306; 147368</t>
+          <t>117574; 148151</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>123367; 175857</t>
+          <t>126462; 177681</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>218063; 271071</t>
+          <t>216491; 266589</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>270525; 328804</t>
+          <t>269655; 326023</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>336819; 394831</t>
+          <t>337935; 394612</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>404153; 452435</t>
+          <t>401959; 455152</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>307100; 365215</t>
+          <t>306145; 367938</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>380464; 441992</t>
+          <t>380695; 446472</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>467049; 530833</t>
+          <t>466259; 531562</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>551405; 619676</t>
+          <t>544289; 619301</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>683327; 776182</t>
+          <t>684726; 776969</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>805280; 907488</t>
+          <t>802590; 906116</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1030310; 1127126</t>
+          <t>1023991; 1131710</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1336940; 1903952</t>
+          <t>1333874; 1898138</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>810669; 909471</t>
+          <t>811432; 910316</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1019795; 1130861</t>
+          <t>1025778; 1138141</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1188552; 1299894</t>
+          <t>1193032; 1296669</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1562609; 2106462</t>
+          <t>1538777; 2107687</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1524012; 1653528</t>
+          <t>1522879; 1655008</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1854323; 2001747</t>
+          <t>1857845; 2006713</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2251771; 2393447</t>
+          <t>2247329; 2396034</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3215788; 3961712</t>
+          <t>3193359; 3968116</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C01-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19C01-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,68%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31,99; 42,02</t>
+          <t>32,22; 42,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,46; 41,87</t>
+          <t>31,39; 41,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45,52; 56,45</t>
+          <t>45,93; 56,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63,59; 71,92</t>
+          <t>63,72; 72,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,35; 47,68</t>
+          <t>35,31; 46,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,9; 51,69</t>
+          <t>39,48; 51,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,32; 58,55</t>
+          <t>47,69; 58,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>62,66; 70,34</t>
+          <t>63,66; 70,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,99; 42,38</t>
+          <t>34,8; 42,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,68; 44,49</t>
+          <t>36,33; 44,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47,99; 55,81</t>
+          <t>48,19; 56,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>64,26; 70,09</t>
+          <t>64,85; 70,48</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,64%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,95; 36,53</t>
+          <t>25,68; 36,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,66; 42,21</t>
+          <t>31,91; 42,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,12; 52,18</t>
+          <t>40,4; 52,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61,45; 70,52</t>
+          <t>60,39; 69,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,31; 43,76</t>
+          <t>32,45; 44,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,76; 51,17</t>
+          <t>40,73; 52,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,39; 59,63</t>
+          <t>48,74; 59,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>63,58; 72,27</t>
+          <t>64,47; 72,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,81; 38,81</t>
+          <t>30,74; 38,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,61; 45,01</t>
+          <t>36,97; 44,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46,45; 54,74</t>
+          <t>46,4; 54,54</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>63,28; 69,38</t>
+          <t>63,37; 69,66</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>55,76%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,18; 32,15</t>
+          <t>22,64; 31,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,76; 30,35</t>
+          <t>22,86; 31,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,92; 43,04</t>
+          <t>33,21; 42,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,16; 57,95</t>
+          <t>50,84; 60,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,54; 43,62</t>
+          <t>26,96; 43,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,58; 38,66</t>
+          <t>26,55; 38,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,86; 41,16</t>
+          <t>25,26; 42,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49,29; 61,91</t>
+          <t>50,17; 62,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,57; 32,87</t>
+          <t>25,56; 33,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25,43; 31,93</t>
+          <t>25,15; 31,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,46; 41,05</t>
+          <t>32,66; 40,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,68; 57,53</t>
+          <t>51,86; 59,53</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>55,82%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,37; 27,19</t>
+          <t>21,64; 27,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,11; 27,08</t>
+          <t>21,12; 26,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,44; 40,14</t>
+          <t>33,62; 40,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48,28; 54,92</t>
+          <t>49,2; 55,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,61; 37,46</t>
+          <t>29,04; 36,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,94; 39,42</t>
+          <t>31,81; 39,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,72; 43,42</t>
+          <t>35,44; 43,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,14; 61,76</t>
+          <t>57,47; 63,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,66; 30,3</t>
+          <t>25,8; 30,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,67; 31,06</t>
+          <t>26,36; 30,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,31; 40,38</t>
+          <t>35,54; 40,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36,74; 56,39</t>
+          <t>53,22; 58,07</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>47,75%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,77; 34,63</t>
+          <t>22,79; 34,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,34; 25,25</t>
+          <t>16,77; 25,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25,97; 35,08</t>
+          <t>25,72; 35,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41,7; 51,86</t>
+          <t>39,77; 49,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,87; 32,9</t>
+          <t>24,64; 33,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,44; 29,5</t>
+          <t>22,34; 29,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,82; 41,92</t>
+          <t>33,65; 41,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>45,18; 62,59</t>
+          <t>47,02; 53,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,26; 32,43</t>
+          <t>25,32; 32,56</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,6; 26,84</t>
+          <t>21,5; 27,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31,43; 37,52</t>
+          <t>31,39; 37,63</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>45,34; 58,22</t>
+          <t>44,79; 50,28</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,52%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37,53; 51,71</t>
+          <t>37,8; 51,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43,94; 57,23</t>
+          <t>44,37; 56,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48,68; 61,33</t>
+          <t>49,17; 61,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54,23; 76,19</t>
+          <t>54,53; 75,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,89; 28,19</t>
+          <t>22,97; 28,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,14; 35,23</t>
+          <t>28,94; 35,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,95; 47,82</t>
+          <t>40,97; 47,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>54,03; 61,18</t>
+          <t>54,4; 61,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,44; 31,78</t>
+          <t>26,42; 31,74</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33,2; 38,94</t>
+          <t>33,0; 38,54</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>43,7; 49,83</t>
+          <t>43,76; 50,06</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>55,7; 63,38</t>
+          <t>56,06; 63,13</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>58,03%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27,95; 31,71</t>
+          <t>27,81; 31,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>27,56; 31,12</t>
+          <t>27,62; 31,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38,56; 42,61</t>
+          <t>38,79; 42,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40,68; 57,9</t>
+          <t>54,94; 58,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,63; 33,24</t>
+          <t>29,65; 33,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,66; 36,23</t>
+          <t>32,57; 35,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,78; 45,41</t>
+          <t>41,61; 45,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>43,96; 60,22</t>
+          <t>57,7; 60,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29,35; 31,9</t>
+          <t>29,26; 31,82</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30,69; 33,15</t>
+          <t>30,69; 33,19</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40,78; 43,47</t>
+          <t>40,92; 43,56</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,11; 58,54</t>
+          <t>56,73; 59,16</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>338416</t>
+          <t>369217</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>294477</t>
+          <t>323518</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>632893</t>
+          <t>692735</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>124042; 162956</t>
+          <t>124938; 164728</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>124383; 165526</t>
+          <t>124109; 165763</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>176436; 218797</t>
+          <t>178029; 218054</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>317417; 359018</t>
+          <t>345504; 390653</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>94845; 127907</t>
+          <t>94745; 126010</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>117289; 151950</t>
+          <t>116059; 151548</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>149439; 184917</t>
+          <t>150599; 185470</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>276292; 310157</t>
+          <t>306427; 341165</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>229538; 278023</t>
+          <t>228314; 278675</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>252853; 306637</t>
+          <t>250397; 307736</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>337592; 392556</t>
+          <t>338948; 394832</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>604120; 658877</t>
+          <t>663807; 721375</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>294433</t>
+          <t>312115</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>255817</t>
+          <t>285775</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>550250</t>
+          <t>597891</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74909; 109676</t>
+          <t>77085; 108866</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>121475; 161963</t>
+          <t>122448; 163595</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>130210; 165226</t>
+          <t>127928; 165120</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>275568; 316233</t>
+          <t>289462; 333518</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>107777; 145980</t>
+          <t>108244; 147355</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>124641; 160404</t>
+          <t>127679; 163342</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>161432; 198920</t>
+          <t>162598; 199218</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>240091; 272882</t>
+          <t>269447; 304068</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>195243; 245958</t>
+          <t>194795; 247001</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255260; 313819</t>
+          <t>257771; 312875</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>302049; 355949</t>
+          <t>301679; 354641</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>522701; 573130</t>
+          <t>568581; 625017</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>234748</t>
+          <t>258000</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91804</t>
+          <t>103693</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>326551</t>
+          <t>361694</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>99732; 138337</t>
+          <t>97422; 136007</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>121870; 162525</t>
+          <t>122413; 167092</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>133406; 174397</t>
+          <t>134590; 173354</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93586; 382921</t>
+          <t>235819; 280591</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>38580; 61094</t>
+          <t>37758; 60848</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63962; 93028</t>
+          <t>63885; 93515</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36049; 57384</t>
+          <t>35221; 58811</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>81315; 102132</t>
+          <t>92737; 115071</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>145809; 187452</t>
+          <t>145774; 188538</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>197369; 247794</t>
+          <t>195160; 244983</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>176770; 223566</t>
+          <t>177895; 222308</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>137756; 474993</t>
+          <t>336403; 386162</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>516766</t>
+          <t>573043</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>457130</t>
+          <t>505725</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>973897</t>
+          <t>1078768</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>186201; 236910</t>
+          <t>188619; 242085</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>205319; 263389</t>
+          <t>205438; 261214</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>294111; 353012</t>
+          <t>295728; 351951</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>481880; 548228</t>
+          <t>539061; 609544</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>176287; 222982</t>
+          <t>172856; 219655</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>222946; 275125</t>
+          <t>221992; 272513</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>244318; 297020</t>
+          <t>242399; 297469</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>241065; 592223</t>
+          <t>480882; 530494</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>376336; 444399</t>
+          <t>378367; 450535</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>445556; 518960</t>
+          <t>440447; 515599</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>552036; 631362</t>
+          <t>555609; 630947</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>719083; 1103506</t>
+          <t>1028530; 1122125</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>203960</t>
+          <t>224422</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>422113</t>
+          <t>397964</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>626073</t>
+          <t>622386</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>56442; 85853</t>
+          <t>56490; 85408</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>69920; 101817</t>
+          <t>67646; 101390</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>110431; 149166</t>
+          <t>109342; 148821</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>183013; 227579</t>
+          <t>202785; 251092</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>113443; 150057</t>
+          <t>112393; 151294</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>150316; 197604</t>
+          <t>149656; 199506</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>188516; 233672</t>
+          <t>187572; 234012</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>367758; 509445</t>
+          <t>373145; 421890</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>177843; 228309</t>
+          <t>178220; 229238</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>231837; 288047</t>
+          <t>230687; 292463</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>308879; 368662</t>
+          <t>308462; 369805</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>568037; 729429</t>
+          <t>583730; 655273</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>153437</t>
+          <t>147805</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>429637</t>
+          <t>473891</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>583074</t>
+          <t>621696</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>79642; 109745</t>
+          <t>80216; 108825</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>97192; 126605</t>
+          <t>98147; 125659</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>117574; 148151</t>
+          <t>118772; 148379</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>126462; 177681</t>
+          <t>123122; 170919</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>216491; 266589</t>
+          <t>217197; 269066</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>269655; 326023</t>
+          <t>267814; 327595</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>337935; 394612</t>
+          <t>338088; 395696</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>401959; 455152</t>
+          <t>445436; 502369</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>306145; 367938</t>
+          <t>305956; 367460</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>380695; 446472</t>
+          <t>378388; 441886</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>466259; 531562</t>
+          <t>466885; 534082</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>544289; 619301</t>
+          <t>585597; 659437</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1741760</t>
+          <t>1884604</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1950979</t>
+          <t>2090567</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3692739</t>
+          <t>3975170</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>684726; 776969</t>
+          <t>681247; 774736</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>802590; 906116</t>
+          <t>804340; 904305</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1023991; 1131710</t>
+          <t>1030263; 1133767</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1333874; 1898138</t>
+          <t>1822358; 1951494</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>811432; 910316</t>
+          <t>812111; 910107</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1025778; 1138141</t>
+          <t>1023094; 1129271</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1193032; 1296669</t>
+          <t>1188231; 1293103</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1538777; 2107687</t>
+          <t>2038719; 2143028</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1522879; 1655008</t>
+          <t>1518224; 1651016</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1857845; 2006713</t>
+          <t>1857710; 2009031</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2247329; 2396034</t>
+          <t>2255306; 2400734</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3193359; 3968116</t>
+          <t>3886140; 4052280</t>
         </is>
       </c>
     </row>
